--- a/2026/week02/commands_windows.xlsx
+++ b/2026/week02/commands_windows.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10911"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alpha/switchdrive/ACT-TP/act-github/act-tp/2022/week02/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Documents/act-2025/act-tp/2026/week02/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC2AB26-0450-9B43-921D-D4B2BEE556D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C2C1CB-28B1-6A48-94FB-4AD252909625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{A06B98F8-6923-9948-94DA-C12D2DC7D968}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{A06B98F8-6923-9948-94DA-C12D2DC7D968}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -80,9 +80,6 @@
     <t>cd</t>
   </si>
   <si>
-    <t>dir /a:h</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -244,6 +241,9 @@
   </si>
   <si>
     <t>change the working directory to be directory</t>
+  </si>
+  <si>
+    <t>dir /a</t>
   </si>
 </sst>
 </file>
@@ -448,38 +448,6 @@
   </cellStyles>
   <dxfs count="8">
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -583,25 +551,57 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -618,21 +618,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{11D3A3B8-F923-8344-99A4-718CF831BECE}" name="Table1" displayName="Table1" ref="A2:C11" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{11D3A3B8-F923-8344-99A4-718CF831BECE}" name="Table1" displayName="Table1" ref="A2:C11" totalsRowShown="0" headerRowDxfId="7" dataDxfId="5" headerRowBorderDxfId="6" tableBorderDxfId="4" totalsRowBorderDxfId="3">
   <autoFilter ref="A2:C11" xr:uid="{11D3A3B8-F923-8344-99A4-718CF831BECE}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D831C0DA-B8AD-514F-8403-B9152C238BFD}" name="MacOS/Linux" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{F0D27EEA-F13B-C341-85FA-FDDE701494D6}" name="Windows" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{9E371E96-1293-2D4B-AA7C-2C406B8D9C75}" name="Description" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{D831C0DA-B8AD-514F-8403-B9152C238BFD}" name="MacOS/Linux" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{F0D27EEA-F13B-C341-85FA-FDDE701494D6}" name="Windows" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{9E371E96-1293-2D4B-AA7C-2C406B8D9C75}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -670,7 +670,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -776,7 +776,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -918,7 +918,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -942,7 +942,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="40" x14ac:dyDescent="0.2">
@@ -953,7 +953,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="38" customHeight="1" x14ac:dyDescent="0.2">
@@ -961,21 +961,21 @@
         <v>0</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="20" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="40" x14ac:dyDescent="0.2">
@@ -983,7 +983,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>2</v>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="9" spans="1:3" ht="20" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>8</v>
@@ -1024,21 +1024,21 @@
     </row>
     <row r="10" spans="1:3" ht="40" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="40" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>23</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>24</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>9</v>
